--- a/工程科學暨創新概論_第35組_BOM.xlsx
+++ b/工程科學暨創新概論_第35組_BOM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian\Desktop\作業(已完成)\大二下\工程創新概論\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brian\Desktop\es-in\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D637FAE2-B854-44AF-83EC-B52F604A9AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8615E7FA-CC20-4B12-852B-32C9F1AD693B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="61">
   <si>
     <r>
       <rPr>
@@ -463,10 +463,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>熱熔槍</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>熱熔膠條</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -475,10 +471,6 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>充電器</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>珍珠板</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -539,18 +531,10 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>18650充電器</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>18650 2x串聯</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>輔助工具</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>7mm 細膠條</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -564,6 +548,45 @@
   </si>
   <si>
     <t>E94146313 李予田</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>自備一顆計一元</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>助教提供</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)+1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>自購</t>
+    </r>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -571,7 +594,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -738,6 +761,13 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="細明體"/>
       <family val="2"/>
       <charset val="136"/>
     </font>
@@ -808,7 +838,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -864,26 +894,29 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1150,7 +1183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1166,32 +1199,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.75" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -1204,13 +1237,13 @@
         <v>26</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>27</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>3</v>
@@ -1259,7 +1292,7 @@
         <v>25</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D5" s="16" t="s">
         <v>28</v>
@@ -1268,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>14</v>
@@ -1292,13 +1325,13 @@
         <v>36</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="8">
         <v>1</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6" s="8">
         <v>0</v>
@@ -1320,13 +1353,13 @@
         <v>30</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" s="8">
         <v>4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G7" s="8">
         <v>0</v>
@@ -1348,13 +1381,13 @@
         <v>32</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E8" s="8">
         <v>1</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G8" s="8">
         <v>0</v>
@@ -1376,13 +1409,13 @@
         <v>35</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E9" s="8">
         <v>4</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G9" s="8">
         <v>0</v>
@@ -1404,13 +1437,13 @@
         <v>31</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="8">
         <v>1</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G10" s="8">
         <v>0</v>
@@ -1432,22 +1465,24 @@
         <v>33</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="8">
+        <v>52</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="8">
         <v>1</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>15</v>
+      <c r="H11" s="26" t="s">
+        <v>57</v>
       </c>
       <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="J11" s="9" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="27.75" customHeight="1">
       <c r="A12" s="15">
@@ -1460,13 +1495,13 @@
         <v>34</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E12" s="8">
         <v>3</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G12" s="8">
         <v>0</v>
@@ -1488,13 +1523,13 @@
         <v>29</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E13" s="8">
         <v>1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G13" s="8">
         <v>0</v>
@@ -1513,16 +1548,16 @@
         <v>17</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E14" s="8">
         <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G14" s="8">
         <v>0</v>
@@ -1541,7 +1576,7 @@
         <v>17</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" s="17">
         <v>18650</v>
@@ -1550,7 +1585,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G15" s="8">
         <v>0</v>
@@ -1563,22 +1598,22 @@
     </row>
     <row r="16" spans="1:10" ht="27.75" customHeight="1">
       <c r="A16" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>17</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" s="8">
         <v>1</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G16" s="8">
         <v>0</v>
@@ -1587,26 +1622,26 @@
         <v>15</v>
       </c>
       <c r="I16" s="9"/>
-      <c r="J16" s="10"/>
-    </row>
-    <row r="17" spans="1:10" ht="27.75" customHeight="1">
+      <c r="J16" s="9"/>
+    </row>
+    <row r="17" spans="1:10" ht="27.6" customHeight="1">
       <c r="A17" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>57</v>
+        <v>39</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="E17" s="8">
         <v>1</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G17" s="8">
         <v>0</v>
@@ -1615,54 +1650,54 @@
         <v>15</v>
       </c>
       <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" ht="27.6" customHeight="1">
       <c r="A18" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="E18" s="8">
         <v>1</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>51</v>
+      <c r="F18" s="8">
+        <v>10</v>
       </c>
       <c r="G18" s="8">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="H18" s="26" t="s">
+        <v>57</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10" ht="27.6" customHeight="1">
       <c r="A19" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" s="17" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>51</v>
+        <v>37</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>55</v>
       </c>
       <c r="E19" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G19" s="8">
         <v>0</v>
@@ -1673,124 +1708,68 @@
       <c r="I19" s="9"/>
       <c r="J19" s="10"/>
     </row>
-    <row r="20" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A20" s="15">
-        <v>16</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8">
-        <v>10</v>
-      </c>
-      <c r="G20" s="8">
-        <v>10</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="10"/>
-    </row>
-    <row r="21" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A21" s="15">
-        <v>17</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="8">
-        <v>2</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="8">
+    <row r="20" spans="1:10" ht="19.2" customHeight="1">
+      <c r="A20" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="20">
+        <f>SUMIF(H5:H19,"自購",G5:G19)</f>
+        <v>11</v>
+      </c>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.2" customHeight="1">
+      <c r="A21" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="20">
+        <v>1500</v>
+      </c>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.2" customHeight="1">
+      <c r="A22" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20">
+        <f>MAX(0,F20-F21)</f>
         <v>0</v>
       </c>
-      <c r="H21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="10"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.2" customHeight="1">
-      <c r="A22" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="22">
-        <f>SUMIF(H5:H21,"自購",G5:G21)</f>
-        <v>10</v>
-      </c>
-      <c r="G22" s="22"/>
-      <c r="H22" s="23" t="s">
-        <v>20</v>
-      </c>
+      <c r="G22" s="20"/>
+      <c r="H22" s="22"/>
       <c r="I22" s="23"/>
       <c r="J22" s="23"/>
     </row>
-    <row r="23" spans="1:10" ht="19.2" customHeight="1">
-      <c r="A23" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="22">
-        <v>1500</v>
-      </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.2" customHeight="1">
-      <c r="A24" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="21"/>
-      <c r="D24" s="21"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22">
-        <f>MAX(0,F22-F23)</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-    </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="H24:J24"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="H21:J21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="F22:G22"/>
     <mergeCell ref="H22:J22"/>
